--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-07-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6C27DC-261A-4CC9-A3C0-97D863E0B56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02395255-744D-4A19-96A6-1B6DD77866BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4650" yWindow="465" windowWidth="21600" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2385" yWindow="1215" windowWidth="21600" windowHeight="10410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -748,9 +748,6 @@
     <t>£51.97</t>
   </si>
   <si>
-    <t>£808.02</t>
-  </si>
-  <si>
     <t>£73.55</t>
   </si>
   <si>
@@ -1202,6 +1199,9 @@
   </si>
   <si>
     <t>£2655.52</t>
+  </si>
+  <si>
+    <t>£37.12</t>
   </si>
 </sst>
 </file>
@@ -1640,7 +1640,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -1664,7 +1664,7 @@
         <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -1696,7 +1696,7 @@
         <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G3" t="s">
         <v>35</v>
@@ -1720,7 +1720,7 @@
         <v>39</v>
       </c>
       <c r="N3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O3" t="s">
         <v>40</v>
@@ -1752,7 +1752,7 @@
         <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G4" t="s">
         <v>46</v>
@@ -1776,7 +1776,7 @@
         <v>51</v>
       </c>
       <c r="N4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O4" t="s">
         <v>52</v>
@@ -1808,7 +1808,7 @@
         <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G5" t="s">
         <v>59</v>
@@ -1832,7 +1832,7 @@
         <v>64</v>
       </c>
       <c r="N5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O5" t="s">
         <v>65</v>
@@ -1864,7 +1864,7 @@
         <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G6" t="s">
         <v>72</v>
@@ -1888,7 +1888,7 @@
         <v>77</v>
       </c>
       <c r="N6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O6" t="s">
         <v>79</v>
@@ -1920,7 +1920,7 @@
         <v>84</v>
       </c>
       <c r="F7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G7" t="s">
         <v>85</v>
@@ -1944,7 +1944,7 @@
         <v>89</v>
       </c>
       <c r="N7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O7" t="s">
         <v>90</v>
@@ -1976,7 +1976,7 @@
         <v>95</v>
       </c>
       <c r="F8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G8" t="s">
         <v>85</v>
@@ -2000,7 +2000,7 @@
         <v>99</v>
       </c>
       <c r="N8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O8" t="s">
         <v>100</v>
@@ -2032,10 +2032,10 @@
         <v>106</v>
       </c>
       <c r="F9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G9" t="s">
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="H9" t="s">
         <v>107</v>
@@ -2056,7 +2056,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O9" t="s">
         <v>111</v>
@@ -2088,7 +2088,7 @@
         <v>116</v>
       </c>
       <c r="F10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G10" t="s">
         <v>117</v>
@@ -2112,7 +2112,7 @@
         <v>122</v>
       </c>
       <c r="N10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O10" t="s">
         <v>123</v>
@@ -2144,7 +2144,7 @@
         <v>129</v>
       </c>
       <c r="F11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G11" t="s">
         <v>130</v>
@@ -2168,7 +2168,7 @@
         <v>134</v>
       </c>
       <c r="N11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O11" t="s">
         <v>135</v>
@@ -2200,7 +2200,7 @@
         <v>141</v>
       </c>
       <c r="F12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G12" t="s">
         <v>142</v>
@@ -2224,7 +2224,7 @@
         <v>147</v>
       </c>
       <c r="N12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O12" t="s">
         <v>148</v>
@@ -2256,7 +2256,7 @@
         <v>153</v>
       </c>
       <c r="F13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G13" t="s">
         <v>154</v>
@@ -2280,7 +2280,7 @@
         <v>159</v>
       </c>
       <c r="N13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O13" t="s">
         <v>160</v>
@@ -2312,7 +2312,7 @@
         <v>166</v>
       </c>
       <c r="F14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G14" t="s">
         <v>167</v>
@@ -2336,7 +2336,7 @@
         <v>172</v>
       </c>
       <c r="N14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O14" t="s">
         <v>173</v>
@@ -2368,7 +2368,7 @@
         <v>143</v>
       </c>
       <c r="F15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G15" t="s">
         <v>179</v>
@@ -2424,7 +2424,7 @@
         <v>190</v>
       </c>
       <c r="F16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G16" t="s">
         <v>191</v>
@@ -2448,7 +2448,7 @@
         <v>196</v>
       </c>
       <c r="N16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O16" t="s">
         <v>197</v>
@@ -2480,7 +2480,7 @@
         <v>203</v>
       </c>
       <c r="F17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G17" t="s">
         <v>143</v>
@@ -2504,7 +2504,7 @@
         <v>207</v>
       </c>
       <c r="N17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O17" t="s">
         <v>208</v>
@@ -2536,7 +2536,7 @@
         <v>213</v>
       </c>
       <c r="F18" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G18" t="s">
         <v>214</v>
@@ -2560,7 +2560,7 @@
         <v>219</v>
       </c>
       <c r="N18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O18" t="s">
         <v>220</v>
@@ -2592,7 +2592,7 @@
         <v>226</v>
       </c>
       <c r="F19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G19" t="s">
         <v>227</v>
@@ -2616,7 +2616,7 @@
         <v>232</v>
       </c>
       <c r="N19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O19" t="s">
         <v>233</v>
@@ -2648,7 +2648,7 @@
         <v>239</v>
       </c>
       <c r="F20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G20" t="s">
         <v>240</v>
@@ -2657,222 +2657,222 @@
         <v>241</v>
       </c>
       <c r="I20" t="s">
+        <v>181</v>
+      </c>
+      <c r="J20" t="s">
         <v>242</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>243</v>
-      </c>
-      <c r="K20" t="s">
-        <v>244</v>
       </c>
       <c r="L20" t="s">
         <v>21</v>
       </c>
       <c r="M20" t="s">
+        <v>244</v>
+      </c>
+      <c r="N20" t="s">
+        <v>385</v>
+      </c>
+      <c r="O20" t="s">
         <v>245</v>
       </c>
-      <c r="N20" t="s">
-        <v>386</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>246</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>247</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>248</v>
-      </c>
-      <c r="R20" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B21" t="s">
         <v>250</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>251</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E21" t="s">
+        <v>251</v>
+      </c>
+      <c r="F21" t="s">
+        <v>364</v>
+      </c>
+      <c r="G21" t="s">
         <v>252</v>
       </c>
-      <c r="D21" t="s">
-        <v>252</v>
-      </c>
-      <c r="E21" t="s">
-        <v>252</v>
-      </c>
-      <c r="F21" t="s">
-        <v>365</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>253</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>254</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>255</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>256</v>
-      </c>
-      <c r="K21" t="s">
-        <v>257</v>
       </c>
       <c r="L21" t="s">
         <v>21</v>
       </c>
       <c r="M21" t="s">
+        <v>257</v>
+      </c>
+      <c r="N21" t="s">
+        <v>385</v>
+      </c>
+      <c r="O21" t="s">
         <v>258</v>
       </c>
-      <c r="N21" t="s">
-        <v>386</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>259</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>260</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>261</v>
-      </c>
-      <c r="R21" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" t="s">
         <v>263</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>264</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>264</v>
+      </c>
+      <c r="E22" t="s">
+        <v>264</v>
+      </c>
+      <c r="F22" t="s">
+        <v>365</v>
+      </c>
+      <c r="G22" t="s">
         <v>265</v>
       </c>
-      <c r="D22" t="s">
-        <v>265</v>
-      </c>
-      <c r="E22" t="s">
-        <v>265</v>
-      </c>
-      <c r="F22" t="s">
-        <v>366</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>266</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>267</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>268</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>269</v>
-      </c>
-      <c r="K22" t="s">
-        <v>270</v>
       </c>
       <c r="L22" t="s">
         <v>21</v>
       </c>
       <c r="M22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N22" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O22" t="s">
         <v>185</v>
       </c>
       <c r="P22" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q22" t="s">
         <v>272</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>273</v>
-      </c>
-      <c r="R22" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>274</v>
+      </c>
+      <c r="B23" t="s">
         <v>275</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>276</v>
       </c>
-      <c r="C23" t="s">
-        <v>277</v>
-      </c>
       <c r="D23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G23" t="s">
         <v>143</v>
       </c>
       <c r="H23" t="s">
+        <v>277</v>
+      </c>
+      <c r="I23" t="s">
         <v>278</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>279</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>280</v>
-      </c>
-      <c r="K23" t="s">
-        <v>281</v>
       </c>
       <c r="L23" t="s">
         <v>21</v>
       </c>
       <c r="M23" t="s">
+        <v>281</v>
+      </c>
+      <c r="N23" t="s">
+        <v>387</v>
+      </c>
+      <c r="O23" t="s">
         <v>282</v>
       </c>
-      <c r="N23" t="s">
-        <v>388</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>283</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>284</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>285</v>
-      </c>
-      <c r="R23" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>286</v>
+      </c>
+      <c r="B24" t="s">
         <v>287</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>288</v>
       </c>
-      <c r="C24" t="s">
-        <v>289</v>
-      </c>
       <c r="D24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G24" t="s">
         <v>143</v>
@@ -2881,51 +2881,51 @@
         <v>175</v>
       </c>
       <c r="I24" t="s">
+        <v>289</v>
+      </c>
+      <c r="J24" t="s">
         <v>290</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>291</v>
-      </c>
-      <c r="K24" t="s">
-        <v>292</v>
       </c>
       <c r="L24" t="s">
         <v>21</v>
       </c>
       <c r="M24" t="s">
+        <v>292</v>
+      </c>
+      <c r="N24" t="s">
+        <v>388</v>
+      </c>
+      <c r="O24" t="s">
         <v>293</v>
       </c>
-      <c r="N24" t="s">
-        <v>389</v>
-      </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>294</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>295</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>296</v>
-      </c>
-      <c r="R24" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>297</v>
+      </c>
+      <c r="B25" t="s">
         <v>298</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>299</v>
       </c>
-      <c r="C25" t="s">
-        <v>300</v>
-      </c>
       <c r="D25" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E25" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F25" t="s">
         <v>143</v>
@@ -2940,7 +2940,7 @@
         <v>143</v>
       </c>
       <c r="J25" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K25" t="s">
         <v>143</v>
@@ -2949,13 +2949,13 @@
         <v>143</v>
       </c>
       <c r="M25" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N25" t="s">
         <v>132</v>
       </c>
       <c r="O25" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P25" t="s">
         <v>143</v>
@@ -2969,226 +2969,226 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>303</v>
+      </c>
+      <c r="B26" t="s">
         <v>304</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>305</v>
       </c>
-      <c r="C26" t="s">
-        <v>306</v>
-      </c>
       <c r="D26" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E26" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F26" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G26" t="s">
         <v>143</v>
       </c>
       <c r="H26" t="s">
+        <v>306</v>
+      </c>
+      <c r="I26" t="s">
         <v>307</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>308</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>309</v>
-      </c>
-      <c r="K26" t="s">
-        <v>310</v>
       </c>
       <c r="L26" t="s">
         <v>21</v>
       </c>
       <c r="M26" t="s">
+        <v>310</v>
+      </c>
+      <c r="N26" t="s">
+        <v>389</v>
+      </c>
+      <c r="O26" t="s">
         <v>311</v>
       </c>
-      <c r="N26" t="s">
-        <v>390</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>312</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>313</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>314</v>
-      </c>
-      <c r="R26" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B27" t="s">
         <v>316</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>317</v>
       </c>
-      <c r="C27" t="s">
-        <v>318</v>
-      </c>
       <c r="D27" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E27" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F27" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G27" t="s">
         <v>143</v>
       </c>
       <c r="H27" t="s">
+        <v>318</v>
+      </c>
+      <c r="I27" t="s">
         <v>319</v>
-      </c>
-      <c r="I27" t="s">
-        <v>320</v>
       </c>
       <c r="J27" t="s">
         <v>143</v>
       </c>
       <c r="K27" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
       </c>
       <c r="M27" t="s">
+        <v>321</v>
+      </c>
+      <c r="N27" t="s">
+        <v>390</v>
+      </c>
+      <c r="O27" t="s">
         <v>322</v>
       </c>
-      <c r="N27" t="s">
-        <v>391</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>323</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>324</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>325</v>
-      </c>
-      <c r="R27" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B28" t="s">
         <v>327</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>328</v>
       </c>
-      <c r="C28" t="s">
-        <v>329</v>
-      </c>
       <c r="D28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G28" t="s">
         <v>143</v>
       </c>
       <c r="H28" t="s">
+        <v>329</v>
+      </c>
+      <c r="I28" t="s">
         <v>330</v>
-      </c>
-      <c r="I28" t="s">
-        <v>331</v>
       </c>
       <c r="J28" t="s">
         <v>143</v>
       </c>
       <c r="K28" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L28" t="s">
         <v>21</v>
       </c>
       <c r="M28" t="s">
+        <v>332</v>
+      </c>
+      <c r="N28" t="s">
+        <v>391</v>
+      </c>
+      <c r="O28" t="s">
         <v>333</v>
       </c>
-      <c r="N28" t="s">
-        <v>392</v>
-      </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>334</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>335</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>336</v>
-      </c>
-      <c r="R28" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>337</v>
+      </c>
+      <c r="B29" t="s">
         <v>338</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>339</v>
       </c>
-      <c r="C29" t="s">
-        <v>340</v>
-      </c>
       <c r="D29" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E29" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F29" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G29" t="s">
         <v>143</v>
       </c>
       <c r="H29" t="s">
+        <v>340</v>
+      </c>
+      <c r="I29" t="s">
         <v>341</v>
-      </c>
-      <c r="I29" t="s">
-        <v>342</v>
       </c>
       <c r="J29" t="s">
         <v>143</v>
       </c>
       <c r="K29" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L29" t="s">
         <v>143</v>
       </c>
       <c r="M29" t="s">
+        <v>343</v>
+      </c>
+      <c r="N29" t="s">
+        <v>392</v>
+      </c>
+      <c r="O29" t="s">
         <v>344</v>
       </c>
-      <c r="N29" t="s">
-        <v>393</v>
-      </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>345</v>
-      </c>
-      <c r="P29" t="s">
-        <v>346</v>
       </c>
       <c r="Q29" t="s">
         <v>143</v>
       </c>
       <c r="R29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
